--- a/filer/56759328_toms.xlsx
+++ b/filer/56759328_toms.xlsx
@@ -5271,11 +5271,21 @@
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="B19" s="16" t="n">
+        <v>22302</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>36556</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>40095</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>41561</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>16800</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -7113,7 +7123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7278,23 +7288,25 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
+          <t>fsa:LongtermDeferredIncome</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n">
-        <v>-18837</v>
-      </c>
-      <c r="E6" s="38" t="n">
-        <v>-3192</v>
-      </c>
-      <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n"/>
-      <c r="H6" s="38" t="n"/>
+          <t>fsa:LongtermDeferredIncome</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n"/>
+      <c r="E6" s="38" t="n"/>
+      <c r="F6" s="38" t="n">
+        <v>32182</v>
+      </c>
+      <c r="G6" s="38" t="n">
+        <v>43431</v>
+      </c>
+      <c r="H6" s="38" t="n">
+        <v>39100</v>
+      </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7309,94 +7321,24 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermDeferredIncome</t>
+          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermDeferredIncome</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n">
-        <v>32182</v>
-      </c>
-      <c r="G7" s="35" t="n">
-        <v>43431</v>
-      </c>
-      <c r="H7" s="35" t="n">
-        <v>39100</v>
-      </c>
+          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>28329</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>6911</v>
+      </c>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="n"/>
+      <c r="H7" s="35" t="n"/>
       <c r="I7" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>fsa:NoncurrentDeferredTaxAssets</t>
-        </is>
-      </c>
-      <c r="C8" s="37" t="inlineStr">
-        <is>
-          <t>fsa:NoncurrentDeferredTaxAssets</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n">
-        <v>22302</v>
-      </c>
-      <c r="E8" s="38" t="n">
-        <v>36556</v>
-      </c>
-      <c r="F8" s="38" t="n">
-        <v>40095</v>
-      </c>
-      <c r="G8" s="38" t="n">
-        <v>41561</v>
-      </c>
-      <c r="H8" s="38" t="n">
-        <v>16800</v>
-      </c>
-      <c r="I8" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>28329</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>6911</v>
-      </c>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
-      <c r="I9" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/56759328_toms.xlsx
+++ b/filer/56759328_toms.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/56759328_toms.xlsx
+++ b/filer/56759328_toms.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_56759328" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_56759328" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_56759328" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_56759328" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1435,35 +1436,35 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
@@ -2673,35 +2674,35 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
@@ -4055,19 +4056,19 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
@@ -4173,19 +4174,19 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
@@ -4482,6 +4483,148 @@
       </c>
       <c r="F92" s="13">
         <f>IFERROR($F$32/($F$54+$F$61)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B95" s="17">
+        <f>'pengestrom_raw_56759328'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C95" s="17">
+        <f>'pengestrom_raw_56759328'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D95" s="17">
+        <f>'pengestrom_raw_56759328'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E95" s="17">
+        <f>'pengestrom_raw_56759328'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F95" s="17">
+        <f>'pengestrom_raw_56759328'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B96" s="17">
+        <f>'pengestrom_raw_56759328'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C96" s="17">
+        <f>'pengestrom_raw_56759328'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D96" s="17">
+        <f>'pengestrom_raw_56759328'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E96" s="17">
+        <f>'pengestrom_raw_56759328'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F96" s="17">
+        <f>'pengestrom_raw_56759328'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw_56759328'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw_56759328'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw_56759328'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw_56759328'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw_56759328'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B98" s="17">
+        <f>'pengestrom_raw_56759328'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C98" s="17">
+        <f>'pengestrom_raw_56759328'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D98" s="17">
+        <f>'pengestrom_raw_56759328'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E98" s="17">
+        <f>'pengestrom_raw_56759328'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F98" s="17">
+        <f>'pengestrom_raw_56759328'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B99">
+        <f>IF(ABS(('pengestrom_raw_56759328'!$B$2+'pengestrom_raw_56759328'!$B$3+'pengestrom_raw_56759328'!$B$4)-'pengestrom_raw_56759328'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_56759328'!$B$2+'pengestrom_raw_56759328'!$B$3+'pengestrom_raw_56759328'!$B$4)-'pengestrom_raw_56759328'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C99">
+        <f>IF(ABS(('pengestrom_raw_56759328'!$C$2+'pengestrom_raw_56759328'!$C$3+'pengestrom_raw_56759328'!$C$4)-'pengestrom_raw_56759328'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_56759328'!$C$2+'pengestrom_raw_56759328'!$C$3+'pengestrom_raw_56759328'!$C$4)-'pengestrom_raw_56759328'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D99">
+        <f>IF(ABS(('pengestrom_raw_56759328'!$D$2+'pengestrom_raw_56759328'!$D$3+'pengestrom_raw_56759328'!$D$4)-'pengestrom_raw_56759328'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_56759328'!$D$2+'pengestrom_raw_56759328'!$D$3+'pengestrom_raw_56759328'!$D$4)-'pengestrom_raw_56759328'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E99">
+        <f>IF(ABS(('pengestrom_raw_56759328'!$E$2+'pengestrom_raw_56759328'!$E$3+'pengestrom_raw_56759328'!$E$4)-'pengestrom_raw_56759328'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_56759328'!$E$2+'pengestrom_raw_56759328'!$E$3+'pengestrom_raw_56759328'!$E$4)-'pengestrom_raw_56759328'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F99">
+        <f>IF(ABS(('pengestrom_raw_56759328'!$F$2+'pengestrom_raw_56759328'!$F$3+'pengestrom_raw_56759328'!$F$4)-'pengestrom_raw_56759328'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_56759328'!$F$2+'pengestrom_raw_56759328'!$F$3+'pengestrom_raw_56759328'!$F$4)-'pengestrom_raw_56759328'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4514,366 +4657,370 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>1398666</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>1602273</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>1777718</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1660868</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>1683500</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>1802100</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>971296</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>1031522</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>1142482</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>1203505</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>1239900</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>1393200</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>427370</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>570751</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>635236</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>457363</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>443600</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>408900</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>379119</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>407105</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>449398</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>310453</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>251600</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>254200</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>74217</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>88547</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>90481</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>97044</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>109500</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>102200</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n">
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n">
         <v>90600</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>1100</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n">
+        <v>2200</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>-25966</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>75099</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>95357</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>49866</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>82500</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>52500</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>67</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>2223</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>33643</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>5500</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>27000</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>40870</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>22418</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>10540</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>12436</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>11500</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>30100</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>-40800</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>-22400</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>-8300</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>21200</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>-6000</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>-3100</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>-66769</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>52681</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>87040</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>71073</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>167100</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>48300</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>-8196</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>-3399</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>15071</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>16734</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>43800</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>7100</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>-58573</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>56080</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>71969</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>54339</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>123300</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>41200</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>933</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>928</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>919</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>902</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>841</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>900</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4904,1013 +5051,995 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n">
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n">
         <v>10670</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>6100</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>4596</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>4195</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>939</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>13100</v>
       </c>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>4818</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>962</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="16" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>10918</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>5558</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>4195</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>11609</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>13100</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>10900</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>323886</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>311875</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>300760</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>325425</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>316900</v>
       </c>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>422483</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>442635</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>417381</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>396952</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>367200</v>
       </c>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>12092</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>17833</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>9191</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>7819</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>12400</v>
       </c>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>35982</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>3682</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>4324</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>7026</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>9900</v>
       </c>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>794443</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>776025</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>731656</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>737222</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>706400</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>761100</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>25037</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>36556</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>40095</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>41561</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>16800</v>
       </c>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>830398</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>818139</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>775946</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>790392</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>736300</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>788600</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>258924</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>235224</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>277756</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>318694</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>285700</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>346300</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>198421</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>203244</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>267076</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>289411</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>290000</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>314700</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>18300</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>13678</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>24761</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>33229</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>11712</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>34400</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>39300</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>22302</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>36556</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>40095</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>41561</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>16800</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>16600</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
-        <v>8282</v>
-      </c>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>3583</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>2261</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>12276</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>500</v>
       </c>
+      <c r="F21" s="17" t="n">
+        <v>5500</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
-        <v>220387</v>
-      </c>
-      <c r="C22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>231588</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>306025</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>313480</v>
       </c>
-      <c r="F22" s="16" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>698</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>725</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>774</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>846</v>
       </c>
-      <c r="F23" s="16" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>6049</v>
-      </c>
-      <c r="C24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>97053</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>31638</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>61553</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>183900</v>
       </c>
+      <c r="F24" s="17" t="n">
+        <v>111500</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>486058</v>
-      </c>
-      <c r="C25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>564590</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>616193</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>694573</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>812800</v>
       </c>
+      <c r="F25" s="17" t="n">
+        <v>817300</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
-        <v>1316456</v>
-      </c>
-      <c r="C26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>1382729</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>1392139</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>1484965</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>1549100</v>
       </c>
+      <c r="F26" s="17" t="n">
+        <v>1605900</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>3500</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>3500</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>3500</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>3500</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <v>3500</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n">
+        <v>11800</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
-        <v>699333</v>
-      </c>
-      <c r="C32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>760033</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>833686</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>904692</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>1033400</v>
       </c>
+      <c r="F32" s="17" t="n">
+        <v>1083100</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
-        <v>702833</v>
-      </c>
-      <c r="C33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>763533</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>837186</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>908192</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>1036900</v>
       </c>
+      <c r="F33" s="17" t="n">
+        <v>1098400</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v>17723</v>
-      </c>
-      <c r="C34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>24445</v>
       </c>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n">
+        <v>37800</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
-        <v>17723</v>
-      </c>
-      <c r="C35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>21447</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>31</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>60338</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>28700</v>
       </c>
+      <c r="F35" s="17" t="n">
+        <v>61700</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
-        <v>172507</v>
-      </c>
-      <c r="C37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>163985</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>155497</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>146860</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>138200</v>
       </c>
+      <c r="F37" s="17" t="n">
+        <v>129100</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v>14663</v>
-      </c>
-      <c r="C39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>14691</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>14781</v>
       </c>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
-        <v>228403</v>
-      </c>
-      <c r="C40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>224568</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="C40" s="17" t="n">
         <v>219131</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>224361</v>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <v>210900</v>
       </c>
+      <c r="F40" s="17" t="n">
+        <v>195000</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
-        <v>55462</v>
-      </c>
-      <c r="C43" s="16" t="n">
+      <c r="B43" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>8488</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>8637</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="E43" s="17" t="n">
         <v>8600</v>
       </c>
+      <c r="F43" s="17" t="n">
+        <v>8900</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
-        <v>192441</v>
-      </c>
-      <c r="C45" s="16" t="n">
+      <c r="B45" s="17" t="n">
         <v>222734</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>210353</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>199080</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>190500</v>
       </c>
+      <c r="F45" s="17" t="n">
+        <v>210000</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="C46" s="16" t="n">
+      <c r="B46" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="C46" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="16" t="n">
+      <c r="E46" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F46" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
-        <v>11016</v>
-      </c>
-      <c r="C48" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>3037</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="C48" s="17" t="n">
         <v>893</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <v>654</v>
       </c>
-      <c r="F48" s="16" t="n">
+      <c r="E48" s="17" t="n">
         <v>9600</v>
       </c>
+      <c r="F48" s="17" t="n">
+        <v>5100</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
-        <v>113233</v>
-      </c>
-      <c r="C50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>153604</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>101918</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>100514</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>81500</v>
       </c>
+      <c r="F50" s="17" t="n">
+        <v>77300</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
-        <v>385220</v>
-      </c>
-      <c r="C52" s="16" t="n">
+      <c r="B52" s="17" t="n">
         <v>394628</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="C52" s="17" t="n">
         <v>335822</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="D52" s="17" t="n">
         <v>352412</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="E52" s="17" t="n">
         <v>301300</v>
       </c>
+      <c r="F52" s="17" t="n">
+        <v>312500</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
-        <v>613623</v>
-      </c>
-      <c r="C53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>619196</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>554953</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>576773</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>512200</v>
       </c>
+      <c r="F53" s="17" t="n">
+        <v>507500</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
-        <v>1316456</v>
-      </c>
-      <c r="C54" s="16" t="n">
+      <c r="B54" s="17" t="n">
         <v>1382729</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>1392139</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>1484965</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="E54" s="17" t="n">
         <v>1549100</v>
+      </c>
+      <c r="F54" s="17" t="n">
+        <v>1605900</v>
       </c>
     </row>
   </sheetData>
@@ -5919,6 +6048,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>204566</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>8925</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>90420</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>95100</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>62900</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-49693</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-48413</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-44375</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>53400</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-130700</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-63842</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-16828</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-17185</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-20100</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-11300</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5949,13 +6200,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6645,7 +6896,7 @@
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -6763,7 +7014,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -6939,7 +7190,7 @@
     <row r="57">
       <c r="A57" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B57" s="29" t="n"/>
@@ -7117,13 +7368,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7162,27 +7413,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7207,10 +7458,10 @@
           <t>fsa:AdjustmentsOfCollateralsBySaleOfInvestments</t>
         </is>
       </c>
-      <c r="D3" s="35" t="n"/>
-      <c r="E3" s="35" t="n">
+      <c r="D3" s="35" t="n">
         <v>256</v>
       </c>
+      <c r="E3" s="35" t="n"/>
       <c r="F3" s="35" t="n"/>
       <c r="G3" s="35" t="n"/>
       <c r="H3" s="35" t="n"/>
@@ -7239,9 +7490,7 @@
       <c r="D4" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="38" t="n">
-        <v>2</v>
-      </c>
+      <c r="E4" s="38" t="n"/>
       <c r="F4" s="38" t="n"/>
       <c r="G4" s="38" t="n"/>
       <c r="H4" s="38" t="n"/>
@@ -7259,21 +7508,21 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:Dividend</t>
+          <t>fsa:DepreciationOfEquity</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:Dividend</t>
+          <t>fsa:DepreciationOfEquity</t>
         </is>
       </c>
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n">
-        <v>-71969</v>
-      </c>
+      <c r="F5" s="35" t="n"/>
       <c r="G5" s="35" t="n"/>
-      <c r="H5" s="35" t="n"/>
+      <c r="H5" s="35" t="n">
+        <v>0</v>
+      </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7288,25 +7537,21 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermDeferredIncome</t>
+          <t>fsa:Dividend</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermDeferredIncome</t>
+          <t>fsa:Dividend</t>
         </is>
       </c>
       <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n">
-        <v>32182</v>
-      </c>
-      <c r="G6" s="38" t="n">
-        <v>43431</v>
-      </c>
-      <c r="H6" s="38" t="n">
-        <v>39100</v>
-      </c>
+      <c r="E6" s="38" t="n">
+        <v>-71969</v>
+      </c>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="38" t="n"/>
+      <c r="H6" s="38" t="n"/>
       <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7321,24 +7566,84 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
+          <t>fsa:ImpairmentLossesAndDepreciationOfActuarialGainsLossesStatementOfChangesInEquity</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n">
-        <v>28329</v>
-      </c>
-      <c r="E7" s="35" t="n">
-        <v>6911</v>
-      </c>
+          <t>fsa:ImpairmentLossesAndDepreciationOfActuarialGainsLossesStatementOfChangesInEquity</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n"/>
       <c r="F7" s="35" t="n"/>
       <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
+      <c r="H7" s="35" t="n">
+        <v>2000</v>
+      </c>
       <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>fsa:LongtermDeferredIncome</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>fsa:LongtermDeferredIncome</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n">
+        <v>32182</v>
+      </c>
+      <c r="F8" s="38" t="n">
+        <v>43431</v>
+      </c>
+      <c r="G8" s="38" t="n">
+        <v>39100</v>
+      </c>
+      <c r="H8" s="38" t="n"/>
+      <c r="I8" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>fsa:ProvisionsForInvestmentsInGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>6911</v>
+      </c>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n"/>
+      <c r="H9" s="35" t="n"/>
+      <c r="I9" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
